--- a/recipients.xlsx
+++ b/recipients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushwam2\Projects\china_news_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A66F8D-B0EA-4A2A-B371-9E11CCEF9151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A3D246-92EF-49D0-BDAD-4F78E547505A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,19 +25,293 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>email</t>
   </si>
   <si>
     <t>okaymahesh@gmail.com</t>
+  </si>
+  <si>
+    <t>rosye.dahal@gmail.com</t>
+  </si>
+  <si>
+    <t>mahesh.kalaiya@gmail.com</t>
+  </si>
+  <si>
+    <t>mahesh.kushwaha2@mail.dcu.ie</t>
+  </si>
+  <si>
+    <t>dineshbhattarai1@gmail.com</t>
+  </si>
+  <si>
+    <t>dkupadhyaynp@gmail.com</t>
+  </si>
+  <si>
+    <t>knadhikari@yahoo.com</t>
+  </si>
+  <si>
+    <t>akarki@gmail.com</t>
+  </si>
+  <si>
+    <t>bhim.udas@gmail.com</t>
+  </si>
+  <si>
+    <t>maskeymk8@gmail.com</t>
+  </si>
+  <si>
+    <t>mohan.lohani64@gmail.com</t>
+  </si>
+  <si>
+    <t>sambins@gmail.com</t>
+  </si>
+  <si>
+    <t>rajbiraj@hotmail.com</t>
+  </si>
+  <si>
+    <t>shresthahl@yahoo.com</t>
+  </si>
+  <si>
+    <t>jayaraj.acharya@gmail.com</t>
+  </si>
+  <si>
+    <t>acharyamra@gmail.com</t>
+  </si>
+  <si>
+    <t>chinasc@mail.com.np</t>
+  </si>
+  <si>
+    <t>rummindei@gmail.com</t>
+  </si>
+  <si>
+    <t>lamsalyubanath@gmail.com</t>
+  </si>
+  <si>
+    <t>dmsingh8@gmail.com</t>
+  </si>
+  <si>
+    <t>bhekhbt@yahoo.com</t>
+  </si>
+  <si>
+    <t>dr.bhusalent@gmail.com</t>
+  </si>
+  <si>
+    <t>riahia@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dawafsherpa@gmail.com </t>
+  </si>
+  <si>
+    <t>rameshorek@gmail.com</t>
+  </si>
+  <si>
+    <t>DurgaPBhattarai@gmail.com</t>
+  </si>
+  <si>
+    <t>sarmilaofnepal@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kailash2005@gmail.com </t>
+  </si>
+  <si>
+    <t>bishwambher@gmail.com</t>
+  </si>
+  <si>
+    <t>pksks2@gmail.com</t>
+  </si>
+  <si>
+    <t>sharmabishnu66@gmail.com</t>
+  </si>
+  <si>
+    <t>chandraghimire8@gmail.com</t>
+  </si>
+  <si>
+    <t>rawoldan@gmail.com</t>
+  </si>
+  <si>
+    <t>deependras2000@gmail.com</t>
+  </si>
+  <si>
+    <t>gbkarkee@hotmail.com</t>
+  </si>
+  <si>
+    <t>kgyawali2012@gmail.com</t>
+  </si>
+  <si>
+    <t>lalshankerghimire@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puruojha@gmail.com </t>
+  </si>
+  <si>
+    <t>smriti1962@gmail.com</t>
+  </si>
+  <si>
+    <t>rssainju@gmail.com</t>
+  </si>
+  <si>
+    <t>rajib.upadhya@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+satishgurung@gmail.com</t>
+  </si>
+  <si>
+    <t>mesuvanga@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hamalyagya@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">durapada@gmail.com </t>
+  </si>
+  <si>
+    <t>upretybk@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sewalamsal@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sushiltiwari01@gmail.com</t>
+  </si>
+  <si>
+    <t>dhawal1961@gmail.com</t>
+  </si>
+  <si>
+    <t>dkgmoen@gmail.com</t>
+  </si>
+  <si>
+    <t>shankar.southasia@gmail.com</t>
+  </si>
+  <si>
+    <t>pushpa605@gmail.com</t>
+  </si>
+  <si>
+    <t>puri_babita011@yahoo.com</t>
+  </si>
+  <si>
+    <t>manjalishakya@gmail.com</t>
+  </si>
+  <si>
+    <t>ird2013.tu@gmail.com</t>
+  </si>
+  <si>
+    <t>gaurav.bhattarai@dird.tu.edu.np</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pandey.lekhanath@gmail.com </t>
+  </si>
+  <si>
+    <t>shahapekshya@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sangeetathapliyal@gmail.com </t>
+  </si>
+  <si>
+    <t>bhaskar.gautam@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bishnu.upreti@gmail.com </t>
+  </si>
+  <si>
+    <t>mrigendrakarki@gmail.com</t>
+  </si>
+  <si>
+    <t>pandeynishchal@hotmail.com</t>
+  </si>
+  <si>
+    <t>paras.kharel@sawtee.org</t>
+  </si>
+  <si>
+    <t>posh.pandey@sawtee.org</t>
+  </si>
+  <si>
+    <t>dr.jaiswal.pramod@gmail.com</t>
+  </si>
+  <si>
+    <t>sohansha@gmail.com</t>
+  </si>
+  <si>
+    <t>sucheta.pyakuryal@iids.org.np</t>
+  </si>
+  <si>
+    <t>sumankarna@hotmail.com</t>
+  </si>
+  <si>
+    <t>swarnim@post.harvard.edu</t>
+  </si>
+  <si>
+    <t>auatnyu@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amishmulmi@gmail.com </t>
+  </si>
+  <si>
+    <t>acharya.anurag@gmail.com</t>
+  </si>
+  <si>
+    <t>bhaskar.koirala@gmail.com</t>
+  </si>
+  <si>
+    <t>tbibek323@gmail.com</t>
+  </si>
+  <si>
+    <t>bhattacd@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nishesh.dhungana@gmail.com </t>
+  </si>
+  <si>
+    <t>pranabkharel@gmail.com</t>
+  </si>
+  <si>
+    <t>rupesh.tha@sawtee.org</t>
+  </si>
+  <si>
+    <t>samar.rana@iids.org.np</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info@nepaleconomicforum.org </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deosaroj@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">saumitra.neupane@pei.center </t>
+  </si>
+  <si>
+    <t>subindra@nepalpeacebuilding.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shreeya.rana@pei.center </t>
+  </si>
+  <si>
+    <t>hari.sharma@purakasia.org</t>
+  </si>
+  <si>
+    <t>dronlamichhane33@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rameshparajuli@gmail.com </t>
+  </si>
+  <si>
+    <t>tikadhakal31@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pukar.malla@daayitwa.org </t>
+  </si>
+  <si>
+    <t>poudyal1997@gmail.com</t>
+  </si>
+  <si>
+    <t>binubeenita@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -53,13 +327,70 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5E5E5E"/>
+      <name val="&quot;Google Sans&quot;"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -75,9 +406,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -359,25 +732,524 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:A95"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="44.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{EBD53FE9-08E0-480A-9339-7EC10107CF99}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{CC00F887-C18B-4B62-8D33-F68D87632F23}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{89FD44CA-0195-45FA-84A8-9CAEDE845225}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{2A0B0F3D-6E2F-4CEB-BF24-9DF127E76F03}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{22BC31AF-89EA-4768-BBBC-5E7861163AC6}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{FAE1D8C6-E3A1-47D4-BD16-3A8FD5931C09}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{D8B62923-691D-4268-861B-4408D4FB36D7}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{13100AF4-0E28-48A1-A0A7-724C49800484}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{ED4C21EF-C581-41FE-869F-A630C3C1CA67}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{45FCC654-531F-43B1-AB75-3936F3A52553}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{83E104DF-8262-404F-9D2A-C125A6E6C690}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{FD01A5F5-7105-410F-888F-5BE232A78DF6}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{E367CEB7-D432-4529-BB3F-FE0861C1728E}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{DA64A023-487E-489D-9C96-812BE833DEDA}"/>
+    <hyperlink ref="A20" r:id="rId15" xr:uid="{8D8F1B68-E768-4540-B095-7FA752053C50}"/>
+    <hyperlink ref="A21" r:id="rId16" xr:uid="{FD5E4371-7A5A-4804-891C-ECD9A96943E2}"/>
+    <hyperlink ref="A22" r:id="rId17" xr:uid="{5BFBBA3B-5502-4EC1-9144-98CC78E0F5DA}"/>
+    <hyperlink ref="A23" r:id="rId18" xr:uid="{416AB09F-E2B0-480C-8A94-28EA7530E900}"/>
+    <hyperlink ref="A30" r:id="rId19" xr:uid="{9AB2DA2C-EE2D-44B7-A550-7D56D677272A}"/>
+    <hyperlink ref="A34" r:id="rId20" xr:uid="{9927803A-C6E7-4E77-91DB-EF21CD9847BE}"/>
+    <hyperlink ref="A38" r:id="rId21" xr:uid="{D426FFE7-CBE7-46C2-AEDB-9A1E1BAF3936}"/>
+    <hyperlink ref="A39" r:id="rId22" xr:uid="{29FC09A1-8B06-475D-BA36-74DA66C9F6A0}"/>
+    <hyperlink ref="A41" r:id="rId23" xr:uid="{8BB1CE22-C851-4D33-893E-6EB49827B14D}"/>
+    <hyperlink ref="A46" r:id="rId24" xr:uid="{6A494F14-14F6-4069-AEF6-5AC0FCB80EDC}"/>
+    <hyperlink ref="A57" r:id="rId25" xr:uid="{24D2C916-E66A-438B-B073-93FB2AC4C1EC}"/>
+    <hyperlink ref="A59" r:id="rId26" xr:uid="{04958CD3-478A-4F76-8D10-3B8BD5B76547}"/>
+    <hyperlink ref="A62" r:id="rId27" xr:uid="{139AF341-FF68-4361-A621-4A897F1E8874}"/>
+    <hyperlink ref="A68" r:id="rId28" xr:uid="{9122DDDB-0A0C-430C-A579-819669AE757B}"/>
+    <hyperlink ref="A72" r:id="rId29" xr:uid="{4651A356-A4A6-4B98-BC87-4A27675B2F4E}"/>
+    <hyperlink ref="A75" r:id="rId30" xr:uid="{28AD9742-7B13-44A9-90AA-04DEA1F2BDC2}"/>
+    <hyperlink ref="A76" r:id="rId31" xr:uid="{82D57AA9-F496-42D7-9378-B9F9DAB260ED}"/>
+    <hyperlink ref="A79" r:id="rId32" xr:uid="{A04908DF-B402-469B-AF7C-FBF7DD2FFBB2}"/>
+    <hyperlink ref="A82" r:id="rId33" xr:uid="{28C4817A-499C-477E-8B66-5F7FC7FF338F}"/>
+    <hyperlink ref="A86" r:id="rId34" xr:uid="{0C53B848-1C62-4D91-9648-0470EA9BB896}"/>
+    <hyperlink ref="A64" r:id="rId35" xr:uid="{2B3137BD-7F39-4190-AF00-72F110BBDF97}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/recipients.xlsx
+++ b/recipients.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushwam2\Projects\china_news_summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushwam2\Projects\daily_geopolitics_monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A3D246-92EF-49D0-BDAD-4F78E547505A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A8BE05-FDBF-4BA0-B6DE-3C5F8781FCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
   <si>
     <t>email</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>binubeenita@gmail.com</t>
+  </si>
+  <si>
+    <t>adhipawankari@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -732,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A95"/>
+  <dimension ref="A1:A96"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="44.6328125" customWidth="1"/>
@@ -1211,6 +1214,11 @@
     <row r="95" spans="1:1">
       <c r="A95" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1250,6 +1258,7 @@
     <hyperlink ref="A82" r:id="rId33" xr:uid="{28C4817A-499C-477E-8B66-5F7FC7FF338F}"/>
     <hyperlink ref="A86" r:id="rId34" xr:uid="{0C53B848-1C62-4D91-9648-0470EA9BB896}"/>
     <hyperlink ref="A64" r:id="rId35" xr:uid="{2B3137BD-7F39-4190-AF00-72F110BBDF97}"/>
+    <hyperlink ref="A96" r:id="rId36" xr:uid="{A2292ECD-2452-4905-AED3-A7D8B48FC40F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/recipients.xlsx
+++ b/recipients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushwam2\Projects\daily_geopolitics_monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A8BE05-FDBF-4BA0-B6DE-3C5F8781FCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F41173E-7179-4CAC-8A45-9CC80C425637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
   <si>
     <t>email</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>gbkarkee@hotmail.com</t>
-  </si>
-  <si>
-    <t>kgyawali2012@gmail.com</t>
   </si>
   <si>
     <t>lalshankerghimire@gmail.com</t>
@@ -271,9 +268,6 @@
     <t>samar.rana@iids.org.np</t>
   </si>
   <si>
-    <t xml:space="preserve">info@nepaleconomicforum.org </t>
-  </si>
-  <si>
     <t xml:space="preserve">deosaroj@gmail.com </t>
   </si>
   <si>
@@ -308,6 +302,9 @@
   </si>
   <si>
     <t>adhipawankari@gmail.com</t>
+  </si>
+  <si>
+    <t>lumanaupreti55@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -735,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A96"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="44.6328125" customWidth="1"/>
@@ -922,7 +919,7 @@
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -932,17 +929,17 @@
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -957,22 +954,22 @@
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="11" t="s">
         <v>46</v>
       </c>
     </row>
@@ -987,52 +984,52 @@
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="14" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="15" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="14" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1042,22 +1039,22 @@
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="16" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="10" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1072,12 +1069,12 @@
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="6" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1087,27 +1084,27 @@
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1117,7 +1114,7 @@
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1127,12 +1124,12 @@
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="6" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1142,83 +1139,73 @@
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="6" t="s">
-        <v>81</v>
+      <c r="A87" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="6" t="s">
-        <v>85</v>
+      <c r="A88" s="9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="17" t="s">
-        <v>87</v>
+      <c r="A90" s="18" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="9" t="s">
-        <v>88</v>
+      <c r="A91" s="19" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="6" t="s">
-        <v>89</v>
+      <c r="A92" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="18" t="s">
-        <v>90</v>
+      <c r="A93" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
+      <c r="A94" s="1" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1243,22 +1230,23 @@
     <hyperlink ref="A23" r:id="rId18" xr:uid="{416AB09F-E2B0-480C-8A94-28EA7530E900}"/>
     <hyperlink ref="A30" r:id="rId19" xr:uid="{9AB2DA2C-EE2D-44B7-A550-7D56D677272A}"/>
     <hyperlink ref="A34" r:id="rId20" xr:uid="{9927803A-C6E7-4E77-91DB-EF21CD9847BE}"/>
-    <hyperlink ref="A38" r:id="rId21" xr:uid="{D426FFE7-CBE7-46C2-AEDB-9A1E1BAF3936}"/>
-    <hyperlink ref="A39" r:id="rId22" xr:uid="{29FC09A1-8B06-475D-BA36-74DA66C9F6A0}"/>
-    <hyperlink ref="A41" r:id="rId23" xr:uid="{8BB1CE22-C851-4D33-893E-6EB49827B14D}"/>
-    <hyperlink ref="A46" r:id="rId24" xr:uid="{6A494F14-14F6-4069-AEF6-5AC0FCB80EDC}"/>
-    <hyperlink ref="A57" r:id="rId25" xr:uid="{24D2C916-E66A-438B-B073-93FB2AC4C1EC}"/>
-    <hyperlink ref="A59" r:id="rId26" xr:uid="{04958CD3-478A-4F76-8D10-3B8BD5B76547}"/>
-    <hyperlink ref="A62" r:id="rId27" xr:uid="{139AF341-FF68-4361-A621-4A897F1E8874}"/>
-    <hyperlink ref="A68" r:id="rId28" xr:uid="{9122DDDB-0A0C-430C-A579-819669AE757B}"/>
-    <hyperlink ref="A72" r:id="rId29" xr:uid="{4651A356-A4A6-4B98-BC87-4A27675B2F4E}"/>
-    <hyperlink ref="A75" r:id="rId30" xr:uid="{28AD9742-7B13-44A9-90AA-04DEA1F2BDC2}"/>
-    <hyperlink ref="A76" r:id="rId31" xr:uid="{82D57AA9-F496-42D7-9378-B9F9DAB260ED}"/>
-    <hyperlink ref="A79" r:id="rId32" xr:uid="{A04908DF-B402-469B-AF7C-FBF7DD2FFBB2}"/>
-    <hyperlink ref="A82" r:id="rId33" xr:uid="{28C4817A-499C-477E-8B66-5F7FC7FF338F}"/>
-    <hyperlink ref="A86" r:id="rId34" xr:uid="{0C53B848-1C62-4D91-9648-0470EA9BB896}"/>
-    <hyperlink ref="A64" r:id="rId35" xr:uid="{2B3137BD-7F39-4190-AF00-72F110BBDF97}"/>
-    <hyperlink ref="A96" r:id="rId36" xr:uid="{A2292ECD-2452-4905-AED3-A7D8B48FC40F}"/>
+    <hyperlink ref="A37" r:id="rId21" xr:uid="{D426FFE7-CBE7-46C2-AEDB-9A1E1BAF3936}"/>
+    <hyperlink ref="A38" r:id="rId22" xr:uid="{29FC09A1-8B06-475D-BA36-74DA66C9F6A0}"/>
+    <hyperlink ref="A40" r:id="rId23" xr:uid="{8BB1CE22-C851-4D33-893E-6EB49827B14D}"/>
+    <hyperlink ref="A45" r:id="rId24" xr:uid="{6A494F14-14F6-4069-AEF6-5AC0FCB80EDC}"/>
+    <hyperlink ref="A56" r:id="rId25" xr:uid="{24D2C916-E66A-438B-B073-93FB2AC4C1EC}"/>
+    <hyperlink ref="A58" r:id="rId26" xr:uid="{04958CD3-478A-4F76-8D10-3B8BD5B76547}"/>
+    <hyperlink ref="A61" r:id="rId27" xr:uid="{139AF341-FF68-4361-A621-4A897F1E8874}"/>
+    <hyperlink ref="A67" r:id="rId28" xr:uid="{9122DDDB-0A0C-430C-A579-819669AE757B}"/>
+    <hyperlink ref="A71" r:id="rId29" xr:uid="{4651A356-A4A6-4B98-BC87-4A27675B2F4E}"/>
+    <hyperlink ref="A74" r:id="rId30" xr:uid="{28AD9742-7B13-44A9-90AA-04DEA1F2BDC2}"/>
+    <hyperlink ref="A75" r:id="rId31" xr:uid="{82D57AA9-F496-42D7-9378-B9F9DAB260ED}"/>
+    <hyperlink ref="A78" r:id="rId32" xr:uid="{A04908DF-B402-469B-AF7C-FBF7DD2FFBB2}"/>
+    <hyperlink ref="A81" r:id="rId33" xr:uid="{28C4817A-499C-477E-8B66-5F7FC7FF338F}"/>
+    <hyperlink ref="A84" r:id="rId34" xr:uid="{0C53B848-1C62-4D91-9648-0470EA9BB896}"/>
+    <hyperlink ref="A63" r:id="rId35" xr:uid="{2B3137BD-7F39-4190-AF00-72F110BBDF97}"/>
+    <hyperlink ref="A93" r:id="rId36" xr:uid="{A2292ECD-2452-4905-AED3-A7D8B48FC40F}"/>
+    <hyperlink ref="A94" r:id="rId37" xr:uid="{44A3E695-5DD2-45E0-8AAF-19A5A62A2328}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
